--- a/가축분뇨관련신고/output/261012_입법영향분석_가축분뇨배출시설신고_법령개정_필요사항.xlsx
+++ b/가축분뇨관련신고/output/261012_입법영향분석_가축분뇨배출시설신고_법령개정_필요사항.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -457,8 +457,8 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="80" customWidth="1" min="6" max="6"/>
-    <col width="190" customWidth="1" min="7" max="7"/>
+    <col width="115" customWidth="1" min="6" max="6"/>
+    <col width="200" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,13 +498,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="341.5" customHeight="1">
+    <row r="2" ht="368.5" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026.9.14.</t>
+          <t>2026.9.14.
+2026.9.11.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -514,7 +515,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>안동시 환경관리과 8급 주무관 송영욱(가축분뇨배출시설 허가·신고, 지도점검, 가축분뇨관련영업자 인허가·지도점검)</t>
+          <t>안동시 환경관리과 8급 주무관 송영욱(가축분뇨배출시설 허가·신고, 지도점검, 가축분뇨관련영업자 인허가·지도점검)
+진천군 환경과 구도원(직급 확인 필요)(가축분뇨 배출시설 인허가 및 지도점검)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -528,27 +530,30 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>[인터뷰 내용] 신고의 처리기간은 법령 본문이 아니라 신고서 서식에만 기재되어 있고, 담당자는 서식에만 있어도 문제없다고 보면서도 수리 여부를 일정 기한 내에 정하도록 하는 간주 규정은 필요하다고 봄. 지위승계·변경 건에서 기한을 넘기는 경우가 있고, 건축허가 의제 협의로 들어오는 건은 건축과가 정한 기한으로 처리됨.
-[발언] 송영욱: "원칙이 정해져 있어요. 신고서를 보면 신고는 5~7일 이렇게 되어 있어요." / 송영욱: "신고서 양식에 적혀 있어요. 어차피 민원인들은 법령 내용을 직접 보기보다는 신고서 서식을 통해 신고하니까, 오히려 거기에만 적혀 있어도 제가 보기엔 문제없을 것 같아요." / (오세영) "수리한 때 효력이 발생한다거나, 며칠 이내에 수리하지 않으면 수리한 것으로 본다는 간주 규정 같은 게 필요하다고 보시나요?" / 송영욱: "필요하죠. 민원인 입장에서는 당연하고요. 공무원 쪽에서도 업무를 제대로 처리 못 하는 경우가 있을 수 있으니까요. 그런 규정이 없으면 공무원이 처리하기 싫어서 미루는 경우도 생길 수 있고요." / 송영욱: "그렇게 처리하려고 하면 기한 맞추기가 쉽지 않더라고요." / 송영욱: "건축과 쪽에서 기한을 정해서 넘겨주거든요. 빨리 처리되면 되는데, 기한을 넘겨서 처리하는 경우도 간혹 있죠." / 송영욱: "협의가 들어오면 저희는 허가증을 만들거나 변경 처리를 하고, 수리했다는 알림을 바로 보내주는 식입니다."</t>
+          <t>[인터뷰 내용] (안동시 환경관리과 8급 주무관 송영욱) 신고의 처리기간은 법령 본문이 아니라 신고서 서식에만 기재되어 있고, 담당자는 서식에만 있어도 문제없다고 보면서도 수리 여부를 일정 기한 내에 정하도록 하는 간주 규정은 필요하다고 봄. 지위승계·변경 건에서 기한을 넘기는 경우가 있고, 건축허가 의제 협의로 들어오는 건은 건축과가 정한 기한으로 처리됨.
+[발언] 송영욱: "원칙이 정해져 있어요. 신고서를 보면 신고는 5~7일 이렇게 되어 있어요." / 송영욱: "신고서 양식에 적혀 있어요. 어차피 민원인들은 법령 내용을 직접 보기보다는 신고서 서식을 통해 신고하니까, 오히려 거기에만 적혀 있어도 제가 보기엔 문제없을 것 같아요." / (오세영) "수리한 때 효력이 발생한다거나, 며칠 이내에 수리하지 않으면 수리한 것으로 본다는 간주 규정 같은 게 필요하다고 보시나요?" / 송영욱: "필요하죠. 민원인 입장에서는 당연하고요. 공무원 쪽에서도 업무를 제대로 처리 못 하는 경우가 있을 수 있으니까요. 그런 규정이 없으면 공무원이 처리하기 싫어서 미루는 경우도 생길 수 있고요." / 송영욱: "그렇게 처리하려고 하면 기한 맞추기가 쉽지 않더라고요." / 송영욱: "건축과 쪽에서 기한을 정해서 넘겨주거든요. 빨리 처리되면 되는데, 기한을 넘겨서 처리하는 경우도 간혹 있죠." / 송영욱: "협의가 들어오면 저희는 허가증을 만들거나 변경 처리를 하고, 수리했다는 알림을 바로 보내주는 식입니다."
+[인터뷰 내용] (진천군 환경과 구도원) 면담자가 법률·시행령에 처리기한 규정이 보이지 않는다고 하자, 담당자는 처리기한이 별지 서식 우측 상단에만 있다고 확인하고 설치신고 7일·변경허가 5일·변경신고 2일이라고 답함(현행 서식과 수치가 다름). 기한 내 처리하며, 접수 시 처리 완료되면 알려준다고 안내함.
+[발언] (오세영) "법률이나 시행령을 보면 신고나 허가에 따라 처분해야 하는 날짜(처리기한) 규정이 안 보이던데요." / 구도원: "그건 서식에 나와 있습니다. 가축분뇨 배출시설 설치신고서 우측 상단에 처리기한이 명시되어 있는데, 설치신고는 7일, 변경허가는 5일, 변경신고는 2일로 별지 서식에 정해져 있습니다." / 구도원: "저희가 특별한 사유 없이는 지연시키기 어렵습니다. 특별한 사유가 없으면 기한 내에 처리하고 회신해야 합니다." / 구도원: "서류를 접수할 때부터 처리 완료되면 알려드린다고 안내하기 때문에, 접수했다고 해서 무조건 끝난 것으로 생각하시지는 않습니다."</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>[현행 규정] 법 제11조제3항: 신고대상 배출시설을 설치하려고 하거나 설치·운영 중인 자는 부령으로 정하는 바에 따라 시장·군수·구청장에게 신고하고, 부령으로 정하는 사항을 변경할 때도 같음. 제5항(2021.4.13. 신설): "그 내용을 검토하여 이 법에 적합하면 신고를 수리하여야 한다". 수리 여부의 통지 기한과 기한 내 미통지 시 수리 간주 규정은 법·시행령·시행규칙 본문 어디에도 없음. 처리기간은 시행규칙 별지 제5호서식 처리기간란(설치신고 5일, 변경신고 2일)과 별지 제2호서식(설치허가 7일, 변경허가 7일, 변경신고 5일)에만 기재. 비교: 법 제15조제2항은 준공검사 합격 여부를 "신청일부터 15일 이내"에 결정·통보하도록 법률에 명시. 법령ID 010297, 현행 법률 공포 2026.3.17. 시행 2026.9.18.(2026.3.17. 개정은 타법개정으로 제11조 문언은 인터뷰 시점과 동일). 시행규칙 공포 2026.8.27. 시행 2026.9.18.
-[문제점] ① 제11조제5항으로 설치신고·변경신고가 수리 필요 신고(행정기본법 제34조)가 되어 수리 전에는 효력이 없는데, 신고인이 언제까지 수리 여부를 알 수 있는지와 기한을 넘기면 어떻게 되는지가 법령 본문에 없음. ② 처리기간이 서식에만 있어 민원처리법 제17조에 따라 행정기관이 임의로 정하는 처리기간과 구별되지 않고, 서식 개정만으로 바뀔 수 있음. 서식 사이에도 변경신고 처리기간이 5일(별지 제2호)과 2일(별지 제5호)로 다르게 병존. ③ 안동시 담당자는 지위승계·변경 건에서 기한을 넘기는 경우가 있고, 건축허가 의제 협의(건축법 제11조제6항, 15일) 경로로 들어오는 건은 서식 처리기간과 다른 기한으로 처리된다고 함. 담당자도 수리 간주 규정이 필요하다고 봄.
+[문제점] ① 제11조제5항으로 설치신고·변경신고가 수리 필요 신고(행정기본법 제34조)가 되어 수리 전에는 효력이 없는데, 신고인이 언제까지 수리 여부를 알 수 있는지와 기한을 넘기면 어떻게 되는지가 법령 본문에 없음. ② 처리기간이 서식에만 있어 민원처리법 제17조에 따라 행정기관이 임의로 정하는 처리기간과 구별되지 않고, 서식 개정만으로 바뀔 수 있음. 서식 사이에도 변경신고 처리기간이 5일(별지 제2호)과 2일(별지 제5호)로 다르게 병존. ③ 안동시 담당자는 지위승계·변경 건에서 기한을 넘기는 경우가 있고, 건축허가 의제 협의(건축법 제11조제6항, 15일) 경로로 들어오는 건은 서식 처리기간과 다른 기한으로 처리된다고 함. 담당자도 수리 간주 규정이 필요하다고 봄. ④ 진천군 담당자도 처리기한의 근거를 법령 본문이 아닌 서식에서 찾고 있고, 말한 기간 수치(설치신고 7일, 변경허가 5일, 변경신고 2일)는 현행 서식과 달라 기간이 서식에만 있어 담당자조차 정확히 인지하기 어려운 상태를 보여줌. 실무는 처리 완료 후 통지(수리 통지)를 전제로 운영되나 그 근거와 기한이 법령에 없음.
 [논거] 행정기본법 제34조에 따라 수리 필요 신고의 효력은 수리 시점에 발생하므로, 수리 여부 결정 기한과 지연 시 효과는 신고인의 권리·의무에 직접 영향을 미치는 사항으로 법률 또는 적어도 법규명령 본문에 두어야 함(예측가능성, 법률유보). 같은 소관부처(기후에너지환경부)의 배출시설 신고인 물환경보전법 제33조제4항·제5항(2018.10.16. 신설)은 부령으로 정하는 기간 내 수리 여부 통지 의무와 기간 경과 시 수리 간주를 법률에 두고 있어, 같은 구조로 건축허가 의제 대상(건축법 제11조제5항제15호·제18호)이기도 한 가축분뇨 배출시설 신고만 서식에 의존하는 것은 체계 정합성에 맞지 않음. 악취방지법 제8조제6항처럼 수리 의무만 둔 입법례도 있으나, 신고제 합리화의 취지(수리 여부·시점의 명확화)에 비추어 통지기한·간주 규정을 두는 쪽이 신고인 보호에 부합.
-[개정 방향] ① 법 제11조제5항에 "시장·군수·구청장은 신고를 받은 날부터 부령으로 정하는 기간 내에 수리 여부를 신고인에게 통지하여야 한다"와 "그 기간 내에 수리 여부 또는 처리기간 연장을 통지하지 아니하면 그 기간이 끝난 날의 다음 날에 신고를 수리한 것으로 본다"(물환경보전법 제33조제4항·제5항 문형)를 추가. ② 시행규칙 제7조에 기간 조항을 신설하여 현행 서식의 5일·2일을 본문으로 옮기고, 별지 제5호·제2호서식의 처리기간란을 본문과 일치시킴(변경신고 5일/2일 불일치 정리). ③ 최소 정비안(부령만): 시행규칙 제7조제3항에 "신고를 받은 날부터 5일(변경신고는 2일) 이내에 수리 여부를 통지하여야 한다"를 신설하고 서식 불일치를 정리. 단, 수리 간주는 법률 사항이므로 ①이 필요. ④ 연번 2(진천) 교차확인, 연번 10(지위승계 신고)과 연계 정비.
-[유의] 민원처리법 제19조제1항에 따라 5일 이하 처리기간은 시간 단위로 계산되고 공휴일·토요일을 빼므로 서식의 "2일"은 근무시간 16시간임. 건축허가 의제로 처리되는 건에는 건축법 제11조제6항의 15일 협의 기간이 적용되어 신고 자체의 처리기간과 이원화되는 점은 국토교통부 협의 필요. 송영욱 주무관은 처리기간이 서식에만 있는 것 자체는 문제없다고 보았고 수리 간주 규정은 필요하다고 보았음(두 발언을 분리 기재). 담당 기간 2개월로 지연 사례의 규모는 미확인. [교차확인] 연번 2(진천 인터뷰)와 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="193" customHeight="1">
+[개정 방향] ① 법 제11조제5항에 "시장·군수·구청장은 신고를 받은 날부터 부령으로 정하는 기간 내에 수리 여부를 신고인에게 통지하여야 한다"와 "그 기간 내에 수리 여부 또는 처리기간 연장을 통지하지 아니하면 그 기간이 끝난 날의 다음 날에 신고를 수리한 것으로 본다"(물환경보전법 제33조제4항·제5항 문형)를 추가. ② 시행규칙 제7조에 기간 조항을 신설하여 현행 서식의 5일·2일을 본문으로 옮기고, 별지 제5호·제2호서식의 처리기간란을 본문과 일치시킴(변경신고 5일/2일 불일치 정리). ③ 최소 정비안(부령만): 시행규칙 제7조제3항에 "신고를 받은 날부터 5일(변경신고는 2일) 이내에 수리 여부를 통지하여야 한다"를 신설하고 서식 불일치를 정리. 단, 수리 간주는 법률 사항이므로 ①이 필요. ④ 연번 6(지위승계 신고)과 연계 정비.
+[유의] 민원처리법 제19조제1항에 따라 5일 이하 처리기간은 시간 단위로 계산되고 공휴일·토요일을 빼므로 서식의 "2일"은 근무시간 16시간임. 건축허가 의제로 처리되는 건에는 건축법 제11조제6항의 15일 협의 기간이 적용되어 신고 자체의 처리기간과 이원화되는 점은 국토교통부 협의 필요. 송영욱 주무관은 처리기간이 서식에만 있는 것 자체는 문제없다고 보았고 수리 간주 규정은 필요하다고 보았음(두 발언을 분리 기재). 안동시 담당자의 담당 기간은 2개월로 지연 사례의 규모는 미확인. 진천군 담당자(구도원)는 처리기한이 서식에 있다는 사실만 확인하고 문제로 제기하지 않았으며("그 기한 안에 처리가 됩니다"), 처리기간 단축 요구나 지연 압박도 없다고 함 → 진천 인터뷰는 사실 확인 성격의 입법사실. 발언의 기간 수치와 서식의 차이는 검토메모에 기록(발언은 고치지 않음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="395.5" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026.9.11.</t>
+          <t>2026.9.14.
+2026.9.11.</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -558,29 +563,32 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>진천군 환경과 구도원(직급 확인 필요)(가축분뇨 배출시설 인허가 및 지도점검)</t>
+          <t>안동시 환경관리과 8급 주무관 송영욱(가축분뇨배출시설 허가·신고, 지도점검, 가축분뇨관련영업자 인허가·지도점검)
+진천군 환경과 구도원(직급 확인 필요)(가축분뇨 배출시설 인허가 및 지도점검)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>가축분뇨의 관리 및 이용에 관한 법률 제11조제3항·제5항
-같은 법 시행규칙 제7조제1항·제3항·제4항, 별지 제5호서식(처리기간란)·별지 제2호서식(처리기간란)
-행정기본법 제34조 / 민원 처리에 관한 법률 제17조·제19조</t>
+          <t>가축분뇨의 관리 및 이용에 관한 법률 제11조제1항·제3항("설치·운영 중인 자" 2015.12.1. 개정으로 삽입)·제4항
+같은 법 제18조제1항제6호, 제49조제1호, 제50조제4호
+법률 제12516호(2014.3.24.) 부칙 제8조, 법률 제15510호(2018.3.20.) 부칙 제10조의2(적법화 특례, 법제처 해석례 23-0126 인용문으로 확인·법령 원문 미대조)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>[인터뷰 내용] 면담자가 법률·시행령에 처리기한 규정이 보이지 않는다고 하자, 담당자는 처리기한이 별지 서식 우측 상단에만 있다고 확인하고 설치신고 7일·변경허가 5일·변경신고 2일이라고 답함(현행 서식과 수치가 다름). 기한 내 처리하며, 접수 시 처리 완료되면 알려준다고 안내함.
-[발언] (오세영) "법률이나 시행령을 보면 신고나 허가에 따라 처분해야 하는 날짜(처리기한) 규정이 안 보이던데요." / 구도원: "그건 서식에 나와 있습니다. 가축분뇨 배출시설 설치신고서 우측 상단에 처리기한이 명시되어 있는데, 설치신고는 7일, 변경허가는 5일, 변경신고는 2일로 별지 서식에 정해져 있습니다." / 구도원: "저희가 특별한 사유 없이는 지연시키기 어렵습니다. 특별한 사유가 없으면 기한 내에 처리하고 회신해야 합니다." / 구도원: "서류를 접수할 때부터 처리 완료되면 알려드린다고 안내하기 때문에, 접수했다고 해서 무조건 끝난 것으로 생각하시지는 않습니다."</t>
+          <t>[인터뷰 내용] (안동시 환경관리과 8급 주무관 송영욱) 법률이 '설치하려고 하거나 설치·운영 중인 자'를 허가·신고 주체로 규정해 사후 허가·신고를 상정하는 것처럼 읽히는 반면 제4항은 허가·신고 없는 사용을 금지함. 담당자는 운영 중 미신고 시설이 지원·축산업 허가를 위해 뒤늦게 신고하는 사례가 있고, 그 경우 과태료·고발 후 수리하되 가축사육제한구역이면 신고 자체가 불가하여 철거해야 한다고 설명. 2017~2024년 적법화 사업으로 지금은 연 10건 미만.
+[발언] (오세영) "법률을 보면 설치하려고 하거나 설치·운영 중인 자는 대통령령으로 정하는 바에 따라 설치 계획서를 내서 허가를 받아야 한다고 되어 있잖아요." / 송영욱: "맞아요. 일단 운영 전에 설치를 하는 게 원칙인데, 옛날에는 의제 협의가 없거나 누락됐거나 해서 먼저 건축물을 짓는 경우가 있었어요. 그 뒤에 이 배출시설에 대한 신고를 해서 허가를 받는 거죠." / 송영욱: "운영은 하고 있는데 신고를 안 하고 있다가, 배출시설 자격증이 필요할 때가 있거든요. 지원을 받거나 축산업 허가를 받으려면 요즘은 축산과에서도 요구합니다. 그러면 무허가로 운영하고 있던 분들이 그때 신고를 하는 거예요. 그러면 과태료를 내거나 고발을 당하는데, 문제는 지금 제한구역으로 지정되어 있으면 그 상태에서는 신고 자체가 안 됩니다." / 송영욱: "요즘에는 한 10건 밑으로 되는데, 예전에는 이런 게 많아서 17년도부터 24년도까지 대대적으로 적법화 사업을 했었어요."
+[인터뷰 내용] (진천군 환경과 구도원) 면담자가 제11조제1항의 '설치·운영 중인 자'와 제4항의 사용 금지가 상충되는 것처럼 보인다고 묻자, 담당자는 2016~2017년경까지 무허가 축사가 많아 환경부가 일정 기간 안에 허가·신고를 받도록 한 양성화(적법화) 제도가 있었고 그 흔적으로 문구가 남은 것 같다고 추정하며, 다시 보니 이상하다고 동의함. 현행 규정상 신고·허가 없이는 공사도 들어갈 수 없다고 확인.
+[발언] (오세영) "이미 설치하고 운영 중인 경우에도 사후에 허가를 받을 수 있다는 의미로 읽히는데, 반면 제4항에서는 "누구든지 허가나 변경신고 없이 설치되거나 변경된 배출시설을 사용해서는 안 되며 사육을 위탁할 수 없다"고 되어 있어, 1항과 4항이 서로 상충되는 것처럼 보입니다." / 구도원: "지금은 거의 불가능하지만, 예전에는 그런 경우가 많았다고 들었습니다. 2016~2017년경까지도 무허가 축사가 많았고, 그래서 환경부에서 이를 양성화(적법화)하는 사업을 진행하기도 했습니다. 무허가 축사가 워낙 많다 보니 이들을 전부 고발할 수는 없어서, 일정 기간을 정해 그 기간 내에 허가나 신고를 받도록 하는 제도가 있었던 것으로 압니다. 아마 그래서 법 조문에 그런 문구(운영 중인 자도 허가 대상)가 남아 있는 게 아닐까 생각합니다." / 구도원: "네, 저도 다시 보니 이상하다고 생각합니다." / (오세영) "어쨌든 지금 현행 규정상으로는 신고나 허가를 받지 않으면 그 시설에 대한 공사도 들어갈 수 없다고 보면 되는 거죠?" / 구도원: "네."</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>[현행 규정] 연번 1과 같음. 법 제11조제5항(2021.4.13. 신설) 수리 의무, 처리기간은 시행규칙 별지 제5호서식(설치신고 5일, 변경신고 2일)·별지 제2호서식(설치허가 7일, 변경허가 7일, 변경신고 5일)에만 기재. 수리 통지 기한·수리 간주 규정 없음.
-[문제점] ① 진천군 담당자도 처리기한의 근거를 법령 본문이 아닌 서식에서 찾고 있음을 확인. ② 담당자가 말한 기간(설치신고 7일, 변경허가 5일, 변경신고 2일)은 현행 서식(설치신고 5일, 변경허가 7일, 변경신고 5일/2일)과 다름 — 기간이 서식에만 있어 담당자조차 정확히 인지하기 어려운 상태를 보여줌. ③ 실무는 처리 완료 후 통지(수리 통지)를 전제로 운영되나 그 근거와 기한이 법령에 없음.
-[논거] 연번 1과 같음(행정기본법 제34조, 물환경보전법 제33조제4항·제5항 입법례).
-[개정 방향] 연번 1 ①~③과 같음. 진천 인터뷰는 입법사실(처리기간의 서식 의존 실태)의 교차확인 자료로 사용.
-[유의] 구도원 주무관은 이를 문제로 제기하지 않았고("그 기한 안에 처리가 됩니다"), 처리기간 단축 요구나 지연 압박도 없다고 함 → 진천 인터뷰만으로는 입법사실이 사실 확인 성격에 그침. 발언의 기간 수치와 서식의 차이는 검토메모에 기록(발언은 고치지 않음). [교차확인] 연번 1(안동 인터뷰)과 동일 쟁점.</t>
+          <t>[현행 규정] 법 제11조제1항: "대통령령으로 정하는 규모 이상의 배출시설을 설치하려고 하거나 설치·운영 중인 자는 … 시장·군수·구청장의 허가를 받아야 한다"(개정 2015.12.1, 2021.4.13). 제3항도 같은 구조로 신고. 제4항: "누구든지 … 허가·변경허가 또는 신고·변경신고 없이 설치되거나 변경된 배출시설을 사용해서는 아니 되며". 2015.3.25. 시행본의 제1항·제3항은 "설치하려는 자"였고, "설치하려고 하거나 설치·운영 중인 자"는 2015.12.1. 개정으로 삽입됨(조문 개정이력 확인). 무허가 설치·사육은 제49조제1호(2년 이하 징역·2천만원 이하 벌금), 미신고 설치·사육은 제50조제4호(1년·1천만원), 제18조제1항제6호 폐쇄·사용중지. 가축사육제한구역 내 무허가·미신고 축사 양성화 특례(법률 제12516호 부칙 제8조: 시행일부터 3년 이내 신청 시 수리 가능, 법률 제15510호 부칙 제10조의2: 2018.3.24.까지 신청 시 일정 기간 폐쇄명령 등 적용 제외)는 기간이 종료됨.
+[문제점] ① 제1항·제3항은 이미 "설치·운영 중인 자"를 허가·신고 주체로 규정해 사후 허가·신고를 상정하는데, 같은 조 제4항과 제49조·제50조는 허가·신고 없는 설치·사용을 금지·처벌하므로 같은 조 안에서 사후 신고를 허용하는 문언과 금지하는 문언이 병존. ② 사후 신고를 받을 때의 심사 기준(제한구역 지정 전 설치 여부 등)과 효과(처벌·행정처분과의 관계, 수리 시까지의 사용)가 본칙에 없고 부칙 특례는 종료되어, 안동시 사례처럼 운영 중 신고가 들어오면 제한구역이면 수리 불가·철거, 아니면 과태료·고발 뒤 수리라는 결론이 법문이 아닌 실무 해석으로 정해짐. ③ 두 인터뷰이 모두 문언이 이상하다고 봄. 진천군 담당자는 2016~2017년경까지의 무허가 축사 양성화 제도의 흔적으로 추정했고, 현행법상 허가·신고 없이는 설치(공사) 자체가 불가하다고 운영하고 있어 본칙 문언(설치·운영 중인 자도 허가·신고 주체)과 실무 운영(설치 전 허가·신고 원칙, 사후 신고는 예외적 양성화)이 일치하지 않음을 확인.
+[논거] 같은 조의 항 사이 충돌은 운영 문제가 아닌 정합성 흠결. 의무 부과와 형벌 구성요건(제49조·제50조)에 연결되는 조문은 명확성 원칙상 수범자가 허용되는 행위(설치 전 신고)와 금지되는 행위(미신고 설치·사용)를 문언으로 구별할 수 있어야 함. "설치·운영 중인 자"가 2015.12.1. 개정으로 삽입된 취지(법 개정·조례 개정으로 새로 대상에 편입된 기존 시설의 포섭인지, 양성화 유도인지)가 본칙 문언에 드러나지 않아 해석 부담이 지자체 담당자에게 전가됨.
+[개정 방향] ① 법 제11조제1항·제3항의 "설치하려고 하거나 설치·운영 중인 자"를 "설치하려는 자"로 환원하고, 법령·조례 개정으로 새로 허가·신고 대상이 된 기존 시설의 허가신청·신고 의무와 기한은 부칙 경과조치 또는 별도 항("… 대상이 된 날부터 ○개월 이내에 허가를 신청하거나 신고하여야 한다")으로 분리. ② 또는 제1항·제3항을 유지하되, "설치·운영 중인 자"의 허가·신고 절차와 제4항·벌칙의 적용 관계(수리 시까지 사용중지 등)를 명시. ③ 하위법령만의 정비안은 없음(법률 사항).
+[유의] 2015.12.1. 개정의 제·개정이유 원문은 미확인(사용자에게 요청) → 삽입 취지가 확인되면 ①·② 가운데 선택이 달라질 수 있음. 적법화 특례 부칙은 법제처 해석례 23-0126의 인용문으로 확인했고 법령 원문은 대조하지 않음. 소관 기후에너지환경부. 안동시 담당자의 담당 기간은 2개월이며 "한 10건 밑으로"는 추정치. 쟁점은 면담자가 제기했고 두 인터뷰이가 동의·배경 설명을 한 것이며, 진천군 담당자의 양성화 제도 설명은 추정("압니다", "생각합니다")으로 부칙 특례의 존재는 해석례로 확인했으나 문구 삽입 경위와의 인과관계는 미확인.</t>
         </is>
       </c>
     </row>
@@ -605,101 +613,18 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>가축분뇨의 관리 및 이용에 관한 법률 제11조제1항·제3항("설치·운영 중인 자" 2015.12.1. 개정으로 삽입)·제4항
-같은 법 제18조제1항제6호, 제49조제1호, 제50조제4호
-법률 제12516호(2014.3.24.) 부칙 제8조, 법률 제15510호(2018.3.20.) 부칙 제10조의2(적법화 특례, 법제처 해석례 23-0126 인용문으로 확인·법령 원문 미대조)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 법률이 '설치하려고 하거나 설치·운영 중인 자'를 허가·신고 주체로 규정해 사후 허가·신고를 상정하는 것처럼 읽히는 반면 제4항은 허가·신고 없는 사용을 금지함. 담당자는 운영 중 미신고 시설이 지원·축산업 허가를 위해 뒤늦게 신고하는 사례가 있고, 그 경우 과태료·고발 후 수리하되 가축사육제한구역이면 신고 자체가 불가하여 철거해야 한다고 설명. 2017~2024년 적법화 사업으로 지금은 연 10건 미만.
-[발언] (오세영) "법률을 보면 설치하려고 하거나 설치·운영 중인 자는 대통령령으로 정하는 바에 따라 설치 계획서를 내서 허가를 받아야 한다고 되어 있잖아요." / 송영욱: "맞아요. 일단 운영 전에 설치를 하는 게 원칙인데, 옛날에는 의제 협의가 없거나 누락됐거나 해서 먼저 건축물을 짓는 경우가 있었어요. 그 뒤에 이 배출시설에 대한 신고를 해서 허가를 받는 거죠." / 송영욱: "운영은 하고 있는데 신고를 안 하고 있다가, 배출시설 자격증이 필요할 때가 있거든요. 지원을 받거나 축산업 허가를 받으려면 요즘은 축산과에서도 요구합니다. 그러면 무허가로 운영하고 있던 분들이 그때 신고를 하는 거예요. 그러면 과태료를 내거나 고발을 당하는데, 문제는 지금 제한구역으로 지정되어 있으면 그 상태에서는 신고 자체가 안 됩니다." / 송영욱: "요즘에는 한 10건 밑으로 되는데, 예전에는 이런 게 많아서 17년도부터 24년도까지 대대적으로 적법화 사업을 했었어요."</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>[현행 규정] 법 제11조제1항: "대통령령으로 정하는 규모 이상의 배출시설을 설치하려고 하거나 설치·운영 중인 자는 … 시장·군수·구청장의 허가를 받아야 한다"(개정 2015.12.1, 2021.4.13). 제3항도 같은 구조로 신고. 제4항: "누구든지 … 허가·변경허가 또는 신고·변경신고 없이 설치되거나 변경된 배출시설을 사용해서는 아니 되며". 2015.3.25. 시행본의 제1항·제3항은 "설치하려는 자"였고, "설치하려고 하거나 설치·운영 중인 자"는 2015.12.1. 개정으로 삽입됨(조문 개정이력 확인). 무허가 설치·사육은 제49조제1호(2년 이하 징역·2천만원 이하 벌금), 미신고 설치·사육은 제50조제4호(1년·1천만원), 제18조제1항제6호 폐쇄·사용중지. 가축사육제한구역 내 무허가·미신고 축사 양성화 특례(법률 제12516호 부칙 제8조: 시행일부터 3년 이내 신청 시 수리 가능, 법률 제15510호 부칙 제10조의2: 2018.3.24.까지 신청 시 일정 기간 폐쇄명령 등 적용 제외)는 기간이 종료됨.
-[문제점] ① 제1항·제3항은 이미 "설치·운영 중인 자"를 허가·신고 주체로 규정해 사후 허가·신고를 상정하는데, 같은 조 제4항과 제49조·제50조는 허가·신고 없는 설치·사용을 금지·처벌하므로 같은 조 안에서 사후 신고를 허용하는 문언과 금지하는 문언이 병존. ② 사후 신고를 받을 때의 심사 기준(제한구역 지정 전 설치 여부 등)과 효과(처벌·행정처분과의 관계, 수리 시까지의 사용)가 본칙에 없고 부칙 특례는 종료되어, 안동시 사례처럼 운영 중 신고가 들어오면 제한구역이면 수리 불가·철거, 아니면 과태료·고발 뒤 수리라는 결론이 법문이 아닌 실무 해석으로 정해짐. ③ 두 인터뷰이 모두 문언이 이상하다고 봄(연번 4).
-[논거] 같은 조의 항 사이 충돌은 운영 문제가 아닌 정합성 흠결. 의무 부과와 형벌 구성요건(제49조·제50조)에 연결되는 조문은 명확성 원칙상 수범자가 허용되는 행위(설치 전 신고)와 금지되는 행위(미신고 설치·사용)를 문언으로 구별할 수 있어야 함. "설치·운영 중인 자"가 2015.12.1. 개정으로 삽입된 취지(법 개정·조례 개정으로 새로 대상에 편입된 기존 시설의 포섭인지, 양성화 유도인지)가 본칙 문언에 드러나지 않아 해석 부담이 지자체 담당자에게 전가됨.
-[개정 방향] ① 법 제11조제1항·제3항의 "설치하려고 하거나 설치·운영 중인 자"를 "설치하려는 자"로 환원하고, 법령·조례 개정으로 새로 허가·신고 대상이 된 기존 시설의 허가신청·신고 의무와 기한은 부칙 경과조치 또는 별도 항("… 대상이 된 날부터 ○개월 이내에 허가를 신청하거나 신고하여야 한다")으로 분리. ② 또는 제1항·제3항을 유지하되, "설치·운영 중인 자"의 허가·신고 절차와 제4항·벌칙의 적용 관계(수리 시까지 사용중지 등)를 명시. ③ 하위법령만의 정비안은 없음(법률 사항). ④ 연번 4(진천) 교차확인.
-[유의] 2015.12.1. 개정의 제·개정이유 원문은 미확인(사용자에게 요청) → 삽입 취지가 확인되면 ①·② 가운데 선택이 달라질 수 있음. 적법화 특례 부칙은 법제처 해석례 23-0126의 인용문으로 확인했고 법령 원문은 대조하지 않음. 소관 기후에너지환경부. 인터뷰이의 담당 기간은 2개월이며 "한 10건 밑으로"는 추정치. [교차확인] 연번 4(진천 인터뷰)와 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="274" customHeight="1">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>2026.9.11.</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>공무원</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>진천군 환경과 구도원(직급 확인 필요)(가축분뇨 배출시설 인허가 및 지도점검)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>가축분뇨의 관리 및 이용에 관한 법률 제11조제1항·제3항·제4항
-법률 제12516호(2014.3.24.) 부칙 제8조, 법률 제15510호(2018.3.20.) 부칙 제10조의2(법제처 해석례 23-0126 인용문으로 확인·법령 원문 미대조)</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 면담자가 제11조제1항의 '설치·운영 중인 자'와 제4항의 사용 금지가 상충되는 것처럼 보인다고 묻자, 담당자는 2016~2017년경까지 무허가 축사가 많아 환경부가 일정 기간 안에 허가·신고를 받도록 한 양성화(적법화) 제도가 있었고 그 흔적으로 문구가 남은 것 같다고 추정하며, 다시 보니 이상하다고 동의함. 현행 규정상 신고·허가 없이는 공사도 들어갈 수 없다고 확인.
-[발언] (오세영) "이미 설치하고 운영 중인 경우에도 사후에 허가를 받을 수 있다는 의미로 읽히는데, 반면 제4항에서는 "누구든지 허가나 변경신고 없이 설치되거나 변경된 배출시설을 사용해서는 안 되며 사육을 위탁할 수 없다"고 되어 있어, 1항과 4항이 서로 상충되는 것처럼 보입니다." / 구도원: "지금은 거의 불가능하지만, 예전에는 그런 경우가 많았다고 들었습니다. 2016~2017년경까지도 무허가 축사가 많았고, 그래서 환경부에서 이를 양성화(적법화)하는 사업을 진행하기도 했습니다. 무허가 축사가 워낙 많다 보니 이들을 전부 고발할 수는 없어서, 일정 기간을 정해 그 기간 내에 허가나 신고를 받도록 하는 제도가 있었던 것으로 압니다. 아마 그래서 법 조문에 그런 문구(운영 중인 자도 허가 대상)가 남아 있는 게 아닐까 생각합니다." / 구도원: "네, 저도 다시 보니 이상하다고 생각합니다." / (오세영) "어쨌든 지금 현행 규정상으로는 신고나 허가를 받지 않으면 그 시설에 대한 공사도 들어갈 수 없다고 보면 되는 거죠?" / 구도원: "네."</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>[현행 규정] 연번 3과 같음. 담당자가 추정한 양성화 제도는 법률 제12516호 부칙 제8조(가축사육제한구역의 배출시설에 관한 특례, 시행일부터 3년)와 법률 제15510호 부칙 제10조의2(2018.3.24.까지 신청 시 특례)로 확인됨. 다만 "설치·운영 중인 자" 문구는 이 특례와 별도로 2015.12.1. 개정으로 본칙에 삽입된 것임(2015.3.25. 시행본은 "설치하려는 자").
-[문제점] 연번 3과 같음. 진천군 담당자는 현행법상 허가·신고 없이는 설치(공사) 자체가 불가하다고 운영하고 있어, 본칙 문언(설치·운영 중인 자도 허가·신고 주체)과 실무 운영(설치 전 허가·신고가 원칙, 사후 신고는 예외적 양성화)이 일치하지 않음을 확인.
-[논거] 연번 3과 같음.
-[개정 방향] 연번 3 ①~③과 같음.
-[유의] 쟁점은 면담자가 제기했고 인터뷰이는 동의·배경 설명을 한 것이므로 진천 인터뷰 단독의 입법사실은 중간 수준. 인터뷰이의 양성화 제도 설명은 추정("압니다", "생각합니다")으로 부칙 특례의 존재는 해석례로 확인했으나 문구 삽입 경위와의 인과관계는 미확인. [교차확인] 연번 3(안동 인터뷰)과 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="301" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>2026.9.14.</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>공무원</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>안동시 환경관리과 8급 주무관 송영욱(가축분뇨배출시설 허가·신고, 지도점검, 가축분뇨관련영업자 인허가·지도점검)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
           <t>가축분뇨의 관리 및 이용에 관한 법률 제11조제2항·제3항 후단·제5항
 같은 법 시행규칙 제6조제1항제1호·제7호(개정 2012.11.20.)·제2항, 제7조제2항제5호
 같은 법 시행령 제6조·별표 1, 제8조·별표 2(양·사슴 사육시설은 신고대상 규모만 존재)</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 허가대상 소 사육시설을 염소로 바꾸면 염소는 신고대상 규모만 있어 신고대상으로 떨어지는데, 축종 변경의 변경신고 규정이 '허가대상 배출시설에 해당하는 경우에만 신고'하도록 되어 있어 변경신고로 처리할 수 있는지 불명확. 안동시는 전임자 해석에 따라 변경신고로 받아주되 조건을 붙이고 있으며, 신규 설치신고로 보면 가축사육제한구역에서는 신고 자체가 불가능해짐. 환경부 질의는 하지 않음.
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>[인터뷰 내용] (안동시 환경관리과 8급 주무관 송영욱) 허가대상 소 사육시설을 염소로 바꾸면 염소는 신고대상 규모만 있어 신고대상으로 떨어지는데, 축종 변경의 변경신고 규정이 '허가대상 배출시설에 해당하는 경우에만 신고'하도록 되어 있어 변경신고로 처리할 수 있는지 불명확. 안동시는 전임자 해석에 따라 변경신고로 받아주되 조건을 붙이고 있으며, 신규 설치신고로 보면 가축사육제한구역에서는 신고 자체가 불가능해짐. 환경부 질의는 하지 않음.
 [발언] 송영욱: "축종 변경의 경우, 규정을 보면 가축의 종류를 변경하는 경우는 변경 신고를 해야 한다고 되어 있고요. 여기 보면, 가축의 종류를 변경한 경우는 변경 신고를 한다고 되어 있는데, 다른 조항을 보면 가축의 종류를 변경하더라도 그 사육시설이 허가 대상 배출시설에 해당되는 경우에만 신고한다고 되어 있거든요." / 송영욱: "지위승계하면서 소에서 염소로 바꾸는 경우가 있는데, 염소는 신고 대상밖에 없거든요. 그러면 원래 허가 대상 배출시설이었는데, 신고 대상으로 바뀌게 되는 거잖아요. 그럴 때 변경 신고를 해도 되는 건지 궁금했는데, 전임자 말로는 이런 경우는 변경 신고가 안 된다는 거였어요." / 송영욱: "저는 원래 기존 허가를 폐업하고 새로 설치 신고를 받아야 한다고 생각했었거든요. 그런데 그렇게 하면, 이미 제한구역으로 묶여 있는 경우에는 아예 설치 신고 자체가 안 되는 거죠. 그런데 변경으로 처리할 수는 있으니까요." / 송영욱: "법상으로는 좀 애매한데, 현실적인 해석으로는 그렇게 처리하고 있어요." / 송영욱: "질의는 따로 안 해본 것 같아요. 환경부에 물어보면 원칙대로 해석해서 아예 안 된다고 할 것 같아요."</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>[현행 규정] 법 제11조제2항: 허가를 받은 자가 부령으로 정하는 중요 사항을 변경하려면 변경허가, "그 밖의 사항"을 변경하려면 변경신고. 시행규칙 제6조제1항(변경신고 사항, 개정 2012.11.20.): 제1호 "배출시설의 규모를 100분의 50 미만으로 증설하는 경우 또는 배출시설의 규모를 축소하여 법 제11조제3항에 따른 신고대상으로 변경되는 경우", 제7호 "사육하는 가축의 종류를 변경하는 경우(가축의 종류를 변경하더라도 그 사육시설이 허가대상 배출시설에 해당하는 경우에만 신고한다)". 제2항: 제1호~제4호·제7호는 변경 전 신고. 신고대상 시설의 변경신고(시행규칙 제7조제2항제5호)도 같은 구조("신고대상배출시설에 해당하는 경우에만 신고"). 시행령 별표 1·2: 양(염소 포함)·사슴 사육시설은 신고대상(200㎡ 이상)만 있고 허가대상 규모가 없음. 변경신고 미이행은 제53조제3항제1호 과태료(100만원 이하), 제18조제1항제7호 행정처분.
 [문제점] ① 허가대상 소 사육시설(축사 900㎡ 이상)을 염소 사육시설로 바꾸면 염소는 허가대상 규모 자체가 없어 반드시 신고대상이 되는데, 제6조제1항제7호 괄호는 축종 변경 후에도 허가대상에 머무는 경우에만 변경신고를 규정하고 제1호는 "규모를 축소하여" 신고대상이 되는 경우만 변경신고로 규정 → 축종 변경으로 신고대상이 되는 경우는 변경신고·신규 설치신고 어느 절차도 문언에 없음. ② 안동시는 변경신고로 수리하되 소로 되돌릴 수 없다는 조건을 붙이고, 신규 설치신고로 보면 가축사육제한구역에서는 신고가 불가능해 결과가 정반대 → 지자체·담당자별 처리 편차와 과태료·행정처분 적용의 불확실. ③ 담당자 스스로 "법상으로는 좀 애매"하다고 평가하며 환경부 질의는 하지 않음.
@@ -709,108 +634,74 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="260.5" customHeight="1">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>2026.9.14.</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+    <row r="5" ht="287.5" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026.9.14.
+2026.9.11.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>공무원</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>안동시 환경관리과 8급 주무관 송영욱(가축분뇨배출시설 허가·신고, 지도점검, 가축분뇨관련영업자 인허가·지도점검)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>안동시 환경관리과 8급 주무관 송영욱(가축분뇨배출시설 허가·신고, 지도점검, 가축분뇨관련영업자 인허가·지도점검)
+진천군 환경과 구도원(직급 확인 필요)(가축분뇨 배출시설 인허가 및 지도점검)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>가축분뇨의 관리 및 이용에 관한 법률 시행령 별표 1 비고 3·4, 별표 2 비고 3~5("동일 사업장" 합산)
 같은 법 제2조제3호, 제11조제1항·제3항, 제12조제2항제2호("연접")
 환경영향평가법 시행령 별표(50m 기준, 인터뷰 발언·원문 미대조)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 허가·신고 대상 판단 시 여러 축사를 합산하는 단위인 '동일 사업장'의 기준이 없어, 담당자가 환경영향평가법의 50m 기준을 검토한 뒤 자체적으로 '인접 필지(지번 연속)' 기준을 세워 운용. 구체적 기준이 없어 그때그때 판단이 달라질 수 있고, 과거 동일 사업장으로 보이는데 별도 허가가 난 사례와 부지를 나누어 마릿수를 분산하는 사례가 있음.
-[발언] 송영욱: "그것도 상당히 모호한 부분이어서, 제가 최근에 여기저기 알아보고 기준을 잡았습니다. 원래 처음에는 환경영향평가법에서 배출시설 면적을 산정하는 기준을 가져와서 적용해 볼까 했어요. 거기 보면 50미터 기준으로 동일 사업장 여부를 판단하거든요." / 송영욱: "그래서 제가 잡은 기준은 인접 필지 여부입니다. 지번이 바로 붙어 있는 사업장, 예를 들어 1번지 2번지처럼 연속되어 있으면 동일 사업장으로 보고, 1, 2, 3번지 중간에 다른 필지나 도로가 끼어 있으면 별도 사업장으로 판단하고 있어요." / 송영욱: "구체적인 기준은 없고, 그때그때 상황에 따라 판단이 달라질 수 있습니다." / 송영욱: "그래서 예전 건을 보면, 이건 동일 사업장인데 어떻게 별도로 허가가 나갔지 싶은 경우도 있고요." / 송영욱: "그렇긴 한데, 그것도 아시는지 모르겠지만 부지를 두세 군데로 나눠서 여기서 40마리, 30마리 이런 식으로 키우는 경우가 있어요. 합치면 규모가 커지는 거죠."</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>[인터뷰 내용] (안동시 환경관리과 8급 주무관 송영욱) 허가·신고 대상 판단 시 여러 축사를 합산하는 단위인 '동일 사업장'의 기준이 없어, 담당자가 환경영향평가법의 50m 기준을 검토한 뒤 자체적으로 '인접 필지(지번 연속)' 기준을 세워 운용. 구체적 기준이 없어 그때그때 판단이 달라질 수 있고, 과거 동일 사업장으로 보이는데 별도 허가가 난 사례와 부지를 나누어 마릿수를 분산하는 사례가 있음.
+[발언] 송영욱: "그것도 상당히 모호한 부분이어서, 제가 최근에 여기저기 알아보고 기준을 잡았습니다. 원래 처음에는 환경영향평가법에서 배출시설 면적을 산정하는 기준을 가져와서 적용해 볼까 했어요. 거기 보면 50미터 기준으로 동일 사업장 여부를 판단하거든요." / 송영욱: "그래서 제가 잡은 기준은 인접 필지 여부입니다. 지번이 바로 붙어 있는 사업장, 예를 들어 1번지 2번지처럼 연속되어 있으면 동일 사업장으로 보고, 1, 2, 3번지 중간에 다른 필지나 도로가 끼어 있으면 별도 사업장으로 판단하고 있어요." / 송영욱: "구체적인 기준은 없고, 그때그때 상황에 따라 판단이 달라질 수 있습니다." / 송영욱: "그래서 예전 건을 보면, 이건 동일 사업장인데 어떻게 별도로 허가가 나갔지 싶은 경우도 있고요." / 송영욱: "그렇긴 한데, 그것도 아시는지 모르겠지만 부지를 두세 군데로 나눠서 여기서 40마리, 30마리 이런 식으로 키우는 경우가 있어요. 합치면 규모가 커지는 거죠."
+[인터뷰 내용] (진천군 환경과 구도원) 같은 사업자가 인접한 여러 동의 축사를 쪼개어 신고로 처리하는 사례는 진천군에 없다고 하면서, '인접'이 어느 정도 거리를 뜻하는지 명확하지 않아 사업장 소재지를 필지 단위로 판단한다고 함.
+[발언] 구도원: "진천군에는 그런 경우가 없습니다. "인접하다"는 것이 정확히 어느 정도 거리를 의미하는지도 명확하지 않고, 저희는 사업장 소재지를 필지 단위로 판단하고 있어서, 도로명이 아니라 정확한 필지 수로 구분합니다." / (오세영) "같은 리(里) 단위는 인접하다고 볼 수 없나요?" / 구도원: "필지로 하다보니까 잘 떠오르지는 않네요."</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>[현행 규정] 시행령 별표 1(허가대상)·별표 2(신고대상) 비고 3: "동일 사업장에 같은 종류의 시설이 둘 이상 있는 경우에는 각 시설의 면적을 합산한 것을 해당 시설의 규모로 한다", 비고 4·5: 다른 종류의 시설·방목 사육시설의 합산 계산식(별표 개정 2015.3.24.). "동일 사업장"의 정의(운영 주체의 동일성, 필지의 연속성, 거리)는 법·시행령·시행규칙에 없음. 법 제12조제2항제2호는 공동처리시설 요건에 "배출시설이 연접하여 위치한 경우"라는 별개 용어를 사용. 시행령 공포·시행 2026.7.28.
-[문제점] ① 허가·신고 의무의 발생 여부가 합산에 따라 달라지는데 합산 단위가 정의되지 않아, 안동시는 담당자가 환경영향평가법의 50m 기준을 검토한 뒤 자체 "인접 필지" 기준을 세웠고 진천군은 "필지 단위"로 판단(연번 7) → 지자체·담당자별 기준 상이. ② 과거 동일 사업장으로 보이는데 별도 허가가 난 사례, 부지를 나누어 마릿수를 분산하는 사례가 있다고 함. ③ 운영 주체의 동일성 판단 자료(가족관계증명서)로는 방계 친족을 확인할 수 없어 담당자 판단에 한계.
+[문제점] ① 허가·신고 의무의 발생 여부가 합산에 따라 달라지는데 합산 단위가 정의되지 않아, 안동시는 담당자가 환경영향평가법의 50m 기준을 검토한 뒤 자체 "인접 필지" 기준을 세웠고 진천군은 "필지 단위"로 판단하면서 "인접"이 어느 정도 거리인지 명확하지 않다고 함 → 지자체·담당자별 기준 상이. ② 과거 동일 사업장으로 보이는데 별도 허가가 난 사례, 부지를 나누어 마릿수를 분산하는 사례가 있다고 함. ③ 운영 주체의 동일성 판단 자료(가족관계증명서)로는 방계 친족을 확인할 수 없어 담당자 판단에 한계.
 [논거] 허가·신고 의무의 성립 요건은 수범자가 예측할 수 있어야 하고(명확성), 같은 사실관계에 지자체마다 다른 의무가 발생하는 것은 법 적용의 통일성·평등원칙 문제. 기존 합산 규정의 적용 단위를 정의하는 것은 규제 신설이 아니라 명확화에 해당하나, 정의의 내용(동일인 범위, 연접의 범위)에 따라 대상이 넓어질 수 있어 경계 사례로 취급.
-[개정 방향] ① 시행령 별표 1·2 비고에 "동일 사업장"의 정의를 신설(예: 같은 사람 또는 같은 법인이 소유·운영하는 배출시설로서 같은 필지 또는 서로 연접한 필지에 설치된 것) — 대통령령 개정으로 가능. ② 거리 기준을 둘 경우 환경영향평가법 시행령의 50m 기준과의 관계를 정리하고, 법 제12조제2항제2호의 "연접"과 용어를 통일. ③ 최소 정비안: 비고에 "동일 사업장의 판단 기준은 기후에너지환경부장관이 정하여 고시한다"를 두고 고시로 기준 제시. ④ 연번 7(진천) 교차확인.
-[유의] 정의의 범위(친족·법인 포함 여부, 연접의 범위)에 따라 허가 대상이 늘어날 수 있어 행정규제기본법상 규제영향 검토 필요 → 본표는 기존 운용 기준(필지 연속성·운영 주체 동일성)의 명시로 한정. 환경영향평가법 50m 기준은 인터뷰 발언으로 원문 미대조. 회피 사례의 규모는 특정되지 않음("법이 완벽할 수는 없으니까요"). [교차확인] 연번 7(진천 인터뷰)과 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="125.5" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>2026.9.11.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+[개정 방향] ① 시행령 별표 1·2 비고에 "동일 사업장"의 정의를 신설(예: 같은 사람 또는 같은 법인이 소유·운영하는 배출시설로서 같은 필지 또는 서로 연접한 필지에 설치된 것) — 대통령령 개정으로 가능. ② 거리 기준을 둘 경우 환경영향평가법 시행령의 50m 기준과의 관계를 정리하고, 법 제12조제2항제2호의 "연접"과 용어를 통일. ③ 최소 정비안: 비고에 "동일 사업장의 판단 기준은 기후에너지환경부장관이 정하여 고시한다"를 두고 고시로 기준 제시.
+[유의] 정의의 범위(친족·법인 포함 여부, 연접의 범위)에 따라 허가 대상이 늘어날 수 있어 행정규제기본법상 규제영향 검토 필요 → 본표는 기존 운용 기준(필지 연속성·운영 주체 동일성)의 명시로 한정. 환경영향평가법 50m 기준은 인터뷰 발언으로 원문 미대조. 회피 사례의 규모는 특정되지 않음("법이 완벽할 수는 없으니까요"). 진천군에는 분할 신고로 허가를 회피한 사례가 없다고 하여("그런 경우가 없습니다") 사례 규모의 입법사실은 안동 인터뷰에 의존하고, 진천 인터뷰는 기준 부재의 확인 자료.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="409" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026.9.14.
+2026.9.11.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>공무원</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>진천군 환경과 구도원(직급 확인 필요)(가축분뇨 배출시설 인허가 및 지도점검)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>가축분뇨의 관리 및 이용에 관한 법률 시행령 별표 1 비고 3·4, 별표 2 비고 3~5("동일 사업장")</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 같은 사업자가 인접한 여러 동의 축사를 쪼개어 신고로 처리하는 사례는 진천군에 없다고 하면서, '인접'이 어느 정도 거리를 뜻하는지 명확하지 않아 사업장 소재지를 필지 단위로 판단한다고 함.
-[발언] 구도원: "진천군에는 그런 경우가 없습니다. "인접하다"는 것이 정확히 어느 정도 거리를 의미하는지도 명확하지 않고, 저희는 사업장 소재지를 필지 단위로 판단하고 있어서, 도로명이 아니라 정확한 필지 수로 구분합니다." / (오세영) "같은 리(里) 단위는 인접하다고 볼 수 없나요?" / 구도원: "필지로 하다보니까 잘 떠오르지는 않네요."</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>[현행 규정] 연번 6과 같음(시행령 별표 1·2 비고의 "동일 사업장" 합산, 정의 없음).
-[문제점] 진천군은 "필지 단위"로, 안동시는 "인접 필지(지번 연속)"로 판단하여 같은 개념에 지자체별 기준이 다름을 확인. 진천군 담당자도 거리 기준의 불명확성을 인정.
-[논거] 연번 6과 같음.
-[개정 방향] 연번 6 ①~③과 같음.
-[유의] 진천군에는 분할 신고로 허가를 회피한 사례가 없다고 하여("그런 경우가 없습니다") 진천 인터뷰 단독의 입법사실은 약함. 기준 부재의 교차확인 자료로만 사용하고, 사례 규모는 안동 인터뷰에 의존. [교차확인] 연번 6(안동 인터뷰)과 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="328" customHeight="1">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2026.9.14.</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>공무원</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>안동시 환경관리과 8급 주무관 송영욱(가축분뇨배출시설 허가·신고, 지도점검, 가축분뇨관련영업자 인허가·지도점검)</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>안동시 환경관리과 8급 주무관 송영욱(가축분뇨배출시설 허가·신고, 지도점검, 가축분뇨관련영업자 인허가·지도점검)
+진천군 환경과 구도원(직급 확인 필요)(가축분뇨 배출시설 인허가 및 지도점검)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>가축분뇨의 관리 및 이용에 관한 법률 제2조제3호
 같은 법 시행규칙 제2조
@@ -818,97 +709,57 @@
 같은 법 제8조제1항(가축사육제한구역 조례 위임)</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 산란계 다단 케이지의 면적을 층별로 합산할지 바닥면적만 볼지에 대해 환경부 유권해석(층별 합산)과 지자체 실무가 갈리고(전국 반반), 인근 영주시는 바닥면적으로 허가한 뒤 주민 소송 중이며 민원인은 바닥면적만 인정한 고등법원 판결을 들어 다툼. 통로·기계실의 포함 여부도 건축과와 달라 현장에서 재산정하며, 과거 통로를 포함하다가 제외로 바뀐 경위가 불명확. 담당자는 조례로 정하면 지역 간 편차가 생긴다고 봄.
-[발언] 송영욱: "소 같은 경우 우사가 있으면 건축 쪽에서는 소가 다니는 전체 면적을 웬만하면 다 보는데, 저희는 그 사이에 사람이 다니는 통로는 배출시설 면적으로 안 봐요." / 송영욱: "중간에 어떤 이유가 있었는지 지금은 빼는 걸로 바뀌었더라고요. 통로 면적이나 기계실 같은 것들이요." / 송영욱: "케이지 사육 방식이 기존 기준에 없다 보니 문제가 되는 거예요. 그래서 많이 키우고 싶어서 케이지를 도입하면, 같은 제한구역 면적 기준으로도 사육 마릿수가 몇 배로 늘어나거든요." / 송영욱: "환경부는 그렇게 해석해요. 그런데 전국적으로 보면 지자체별로 반반 정도예요. 그렇게 층수를 다 합산하는 곳도 있고 안 하는 곳도 있고요." / 송영욱: "유권해석은 그렇게 나왔는데, 좀 이상한 게 광주에서는 고등법원에서 판결이 바닥 면적만 인정하는 식으로 나왔어요." / 송영욱: "그래서 보면, 인근 영주시는 케이지가 아니라 바닥 면적으로 허가를 내줬는데, 민원인이 어떻게 알았는지 '왜 이렇게 허가를 내줬냐, 허가를 취소하라'고 해서 지금 소송이 진행 중이에요." / 송영욱: "저는 이걸 조례로 정하는 게 좋다고 생각했는데, 조례로 하다 보니 이런 문제가 생기더라고요. 이 업 하시는 분들은 한 군데서만 하는 게 아니라 여러 지역에서 하시거든요."</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>[인터뷰 내용] (안동시 환경관리과 8급 주무관 송영욱) 산란계 다단 케이지의 면적을 층별로 합산할지 바닥면적만 볼지에 대해 환경부 유권해석(층별 합산)과 지자체 실무가 갈리고(전국 반반), 인근 영주시는 바닥면적으로 허가한 뒤 주민 소송 중이며 민원인은 바닥면적만 인정한 고등법원 판결을 들어 다툼. 통로·기계실의 포함 여부도 건축과와 달라 현장에서 재산정하며, 과거 통로를 포함하다가 제외로 바뀐 경위가 불명확. 담당자는 조례로 정하면 지역 간 편차가 생긴다고 봄.
+[발언] 송영욱: "소 같은 경우 우사가 있으면 건축 쪽에서는 소가 다니는 전체 면적을 웬만하면 다 보는데, 저희는 그 사이에 사람이 다니는 통로는 배출시설 면적으로 안 봐요." / 송영욱: "중간에 어떤 이유가 있었는지 지금은 빼는 걸로 바뀌었더라고요. 통로 면적이나 기계실 같은 것들이요." / 송영욱: "케이지 사육 방식이 기존 기준에 없다 보니 문제가 되는 거예요. 그래서 많이 키우고 싶어서 케이지를 도입하면, 같은 제한구역 면적 기준으로도 사육 마릿수가 몇 배로 늘어나거든요." / 송영욱: "환경부는 그렇게 해석해요. 그런데 전국적으로 보면 지자체별로 반반 정도예요. 그렇게 층수를 다 합산하는 곳도 있고 안 하는 곳도 있고요." / 송영욱: "유권해석은 그렇게 나왔는데, 좀 이상한 게 광주에서는 고등법원에서 판결이 바닥 면적만 인정하는 식으로 나왔어요." / 송영욱: "그래서 보면, 인근 영주시는 케이지가 아니라 바닥 면적으로 허가를 내줬는데, 민원인이 어떻게 알았는지 '왜 이렇게 허가를 내줬냐, 허가를 취소하라'고 해서 지금 소송이 진행 중이에요." / 송영욱: "저는 이걸 조례로 정하는 게 좋다고 생각했는데, 조례로 하다 보니 이런 문제가 생기더라고요. 이 업 하시는 분들은 한 군데서만 하는 게 아니라 여러 지역에서 하시거든요."
+[인터뷰 내용] (진천군 환경과 구도원) 다단 케이지 양계장의 면적을 층별로 합산할지 지자체마다 해석이 다르고 최근 환경부 유권해석은 층별 합산 입장이라고 함. 담당자는 축사 내 먹이통·사람 통로의 포함 여부 등 면적 산정 시 포함할 것과 제외할 것을 구분하는 기준을 지침 수준에서라도 명확히 해 달라고 요청하며, 신축 시에도 면적 산정 문제로 위법 상황이 생긴다고 함.
+[발언] 구도원: "이 케이지가 여러 층 구조일 때 이를 면적에 어떻게 반영할지가 지자체마다 해석이 다릅니다. 어느 지자체는 층수와 무관하게 바닥면적만 본다고 하고, 어느 지자체는 층마다 면적을 합산해야 한다(바닥이 1000㎡면 7층일 때 7000㎡로 산정)고 봅니다." / 구도원: "최근 환경부 유권해석도 층마다 포함하라는 입장이어서, 이런 부분에서 지자체마다 면적 산정 방식에 차이가 있을 수 있습니다." / 구도원: "배출시설의 면적을 좀 더 정확히 산정할 수 있는 지침이 있으면 좋겠습니다." / 구도원: "면적 산정 시 포함할 것과 제외할 것을 구분해 주는 기준을 말씀드리는 겁니다. 어떻게 보면 다양한데, 예를 들어 축사 내 먹이통 같은 것을 면적에 포함해야 하는지, 축사 내부에 사람이 다니는 통로는 제외해야 하는지 등이 다소 애매합니다. 법령에 아주 구체적으로 명시하기는 어렵더라도, 지침 수준에서라도 명확히 해 주시면 좋겠습니다." / 구도원: "뚜렷하게 분리된 경우는 아닙니다. 신축 시에도 이런 면적 산정 문제로 다소 위법한 상황이 발생하기도 해서, 애매한 부분들이 남아 있습니다."</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>[현행 규정] 법 제2조제3호: "배출시설"이란 가축의 사육으로 인하여 가축분뇨가 발생하는 시설 및 장소 등으로서 축사·운동장, 그 밖에 부령으로 정하는 것. 시행규칙 제2조: 착유실, 먹이방, 분만실, 방목지. 시행령 별표 1·2는 허가·신고 대상을 축종별 "면적 ○㎡ 이상"으로 정하나(닭·오리 3,000㎡ 이상 허가, 200㎡ 이상 신고 등) 면적의 산정 방법(바닥면적인지, 다단 사육시설의 층별 면적을 합산하는지, 통로·기계실·관리사를 제외하는지)은 규정하지 않음. 비고 2는 운동장(1일 8시간 이상 상시 체류 시 축사로 봄)만 규정. 별표 개정 2015.3.24.
-[문제점] ① 산란계 다단 케이지: 환경부 유권해석은 층별 합산인데 지자체 실무는 "반반"이고, 인근 영주시는 바닥면적으로 허가한 뒤 주민이 환경부 해석을 근거로 허가 취소 소송 중, 안동시 민원인은 바닥면적만 인정한 고등법원 판결을 들어 다툼 → 같은 시설이 지자체에 따라 허가·신고 대상 여부와 가축사육제한구역 조례의 면적 기준 적용이 달라짐. ② 통로·기계실·관리사의 포함 여부가 건축법상 면적과 달라 현장에서 다시 산정하며, 과거 통로를 포함했다가 제외하게 된 경위가 법령에 없음. ③ 진천군도 포함·제외 기준을 지침 수준에서라도 정해 달라고 요청(연번 9).
+[문제점] ① 산란계 다단 케이지: 환경부 유권해석은 층별 합산인데 지자체 실무는 "반반"이고, 인근 영주시는 바닥면적으로 허가한 뒤 주민이 환경부 해석을 근거로 허가 취소 소송 중, 안동시 민원인은 바닥면적만 인정한 고등법원 판결을 들어 다툼 → 같은 시설이 지자체에 따라 허가·신고 대상 여부와 가축사육제한구역 조례의 면적 기준 적용이 달라짐. ② 통로·기계실·관리사의 포함 여부가 건축법상 면적과 달라 현장에서 다시 산정하며, 과거 통로를 포함했다가 제외하게 된 경위가 법령에 없음. ③ 진천군 담당자도 다단 케이지의 층별 합산 여부가 지자체마다 다르다고 확인하고, 먹이통·통로 등 포함·제외 기준이 애매하여 신축 시 위법 상황이 생긴다며 지침 수준에서라도 기준을 정해 달라고 요청 → 최소한 산정 기준을 정할 수 있는 법령상 근거(고시 위임)가 필요.
 [논거] 면적은 허가·신고의 구분, 가축사육제한구역 조례의 규모 기준, 환경영향평가 대상 판단의 공통 변수이므로 산정 방법은 의무 발생 요건의 핵심 요소임. 유권해석으로 운용할 수 있는 사항이기는 하나(제외기준 2), 해석이 지자체 사이에 통일되지 않고 사법 판단과 다르다는 주장이 제기되어 소송이 진행 중인 상태는 해석으로 해소되지 않음. 지자체 조례에 맡기면 "저기서는 되는데 왜 여기는"이라는 편차가 고정되므로 상위 법령에 통일 기준이 필요.
-[개정 방향] ① 시행령 별표 1·2 비고에 면적 산정 원칙을 신설(산정 대상 공간의 범위, 다단 사육시설의 층별 합산 여부, 제외 공간) — 대통령령 개정. ② 세부 산정 기준은 부령 또는 고시에 위임하는 근거를 비고에 둠. ③ 최소 정비안: 비고에 "면적의 산정 방법은 기후에너지환경부장관이 정하여 고시한다" 1문을 추가하고 현행 유권해석 내용을 고시로 정함. ④ 연번 9(진천) 교차확인.
-[유의] 층별 합산을 명시하면 허가 대상이 늘어나는 규제 강화, 바닥면적만으로 명시하면 완화로 작용하므로 행정규제기본법상 규제영향분석과 농림축산식품부(사육 마릿수 정책) 협의 필요 → 본표는 "산정 방법을 법령에 명시"까지만 제안하고 내용은 정책 판단으로 남김(사용자 판단 요청 항목). 환경부 유권해석 원문과 광주고등법원 판결(2014~2019년, 인터뷰이 기억)은 미확인이며 법령정보센터 판례 검색으로 찾지 못함. 영주시 소송은 진행 중이라는 발언만 있음. [교차확인] 연번 9(진천 인터뷰)와 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="274" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>2026.9.11.</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+[개정 방향] ① 시행령 별표 1·2 비고에 면적 산정 원칙을 신설(산정 대상 공간의 범위, 다단 사육시설의 층별 합산 여부, 제외 공간) — 대통령령 개정. ② 세부 산정 기준은 부령 또는 고시에 위임하는 근거를 비고에 둠. ③ 최소 정비안: 비고에 "면적의 산정 방법은 기후에너지환경부장관이 정하여 고시한다" 1문을 추가하고 현행 유권해석 내용을 고시로 정함(진천군 담당자의 '지침 수준' 요청에 대응).
+[유의] 층별 합산을 명시하면 허가 대상이 늘어나는 규제 강화, 바닥면적만으로 명시하면 완화로 작용하므로 행정규제기본법상 규제영향분석과 농림축산식품부(사육 마릿수 정책) 협의 필요 → 본표는 "산정 방법을 법령에 명시"까지만 제안하고 내용은 정책 판단으로 남김(사용자 판단 요청 항목). 환경부 유권해석 원문과 광주고등법원 판결(2014~2019년, 인터뷰이 기억)은 미확인이며 법령정보센터 판례 검색으로 찾지 못함. 영주시 소송은 진행 중이라는 발언만 있음. 진천군 담당자는 통로 제외 여부에 대해 "업무를 편하게 처리하려면 포함하는 것이 맞는 것 같고, 좀 더 명확하게 하려면 제외하는 것이 맞을 것 같다"고 하여 방향을 정하지 않음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="274" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026.9.14.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>공무원</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>진천군 환경과 구도원(직급 확인 필요)(가축분뇨 배출시설 인허가 및 지도점검)</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>가축분뇨의 관리 및 이용에 관한 법률 제2조제3호
-같은 법 시행규칙 제2조
-같은 법 시행령 별표 1·별표 2(규모 기준 "면적")</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 다단 케이지 양계장의 면적을 층별로 합산할지 지자체마다 해석이 다르고 최근 환경부 유권해석은 층별 합산 입장이라고 함. 담당자는 축사 내 먹이통·사람 통로의 포함 여부 등 면적 산정 시 포함할 것과 제외할 것을 구분하는 기준을 지침 수준에서라도 명확히 해 달라고 요청하며, 신축 시에도 면적 산정 문제로 위법 상황이 생긴다고 함.
-[발언] 구도원: "이 케이지가 여러 층 구조일 때 이를 면적에 어떻게 반영할지가 지자체마다 해석이 다릅니다. 어느 지자체는 층수와 무관하게 바닥면적만 본다고 하고, 어느 지자체는 층마다 면적을 합산해야 한다(바닥이 1000㎡면 7층일 때 7000㎡로 산정)고 봅니다." / 구도원: "최근 환경부 유권해석도 층마다 포함하라는 입장이어서, 이런 부분에서 지자체마다 면적 산정 방식에 차이가 있을 수 있습니다." / 구도원: "배출시설의 면적을 좀 더 정확히 산정할 수 있는 지침이 있으면 좋겠습니다." / 구도원: "면적 산정 시 포함할 것과 제외할 것을 구분해 주는 기준을 말씀드리는 겁니다. 어떻게 보면 다양한데, 예를 들어 축사 내 먹이통 같은 것을 면적에 포함해야 하는지, 축사 내부에 사람이 다니는 통로는 제외해야 하는지 등이 다소 애매합니다. 법령에 아주 구체적으로 명시하기는 어렵더라도, 지침 수준에서라도 명확히 해 주시면 좋겠습니다." / 구도원: "뚜렷하게 분리된 경우는 아닙니다. 신축 시에도 이런 면적 산정 문제로 다소 위법한 상황이 발생하기도 해서, 애매한 부분들이 남아 있습니다."</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>[현행 규정] 연번 8과 같음(법 제2조제3호, 시행규칙 제2조, 시행령 별표 1·2의 "면적" 기준에 산정 방법 없음).
-[문제점] ① 진천군 담당자도 다단 케이지의 층별 합산 여부가 지자체마다 다르다고 확인하고, 먹이통·통로 등 포함·제외 기준이 애매하여 신축 시 위법 상황이 생긴다고 함. ② 담당자는 법령 명시가 어렵다면 지침 수준이라도 요구 → 최소한 산정 기준을 정할 수 있는 법령상 근거(고시 위임)가 필요.
-[논거] 연번 8과 같음.
-[개정 방향] 연번 8 ①~③과 같음. 진천 담당자의 요청(지침 수준)에 대응하는 것이 연번 8의 최소 정비안(③ 고시 위임 근거 신설)임.
-[유의] 담당자는 통로 제외 여부에 대해 "업무를 편하게 처리하려면 포함하는 것이 맞는 것 같고, 좀 더 명확하게 하려면 제외하는 것이 맞을 것 같다"고 하여 방향을 정하지 않음. 환경부 유권해석 원문 미확인. 규제영향 검토 필요성은 연번 8과 같음. [교차확인] 연번 8(안동 인터뷰)과 동일 쟁점.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="287.5" customHeight="1">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2026.9.14.</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>공무원</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>안동시 환경관리과 8급 주무관 송영욱(가축분뇨배출시설 허가·신고, 지도점검, 가축분뇨관련영업자 인허가·지도점검)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>가축분뇨의 관리 및 이용에 관한 법률 제14조제1항·제3항, 제11조제5항(수리 대상에 제14조제3항 신고 미포함), 제53조제3항제4호
 같은 법 시행규칙 제11조의3, 별지 제7호서식(처리기간 7일, 처리절차 접수→검토→결재→통지, 작성방법 "설치신고 수리일")
 행정절차법 제40조 / 행정기본법 제34조 / 민원 처리에 관한 법률 제10조</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>[인터뷰 내용] 지위승계가 끝나면 양도인의 불법 증축 등 책임을 양수인이 떠안게 되어 담당자는 승계 신고 때 현장 확인을 나가며, 현장이 멀면 하루 안에 확인하지 못해 기한을 맞추기 어렵다고 함. 비전자(방문) 접수인 승계 건은 민원실 접수 시점을 조정하기도 함. 전임자는 승계 시 토지·건물 등기 서류를 받았음.
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>[인터뷰 내용] (안동시 환경관리과 8급 주무관 송영욱) 지위승계가 끝나면 양도인의 불법 증축 등 책임을 양수인이 떠안게 되어 담당자는 승계 신고 때 현장 확인을 나가며, 현장이 멀면 하루 안에 확인하지 못해 기한을 맞추기 어렵다고 함. 비전자(방문) 접수인 승계 건은 민원실 접수 시점을 조정하기도 함. 전임자는 승계 시 토지·건물 등기 서류를 받았음.
 [발언] 송영욱: "그게, 전임자가 불법 증축을 해놨으면 그 책임을 전임자에게 지워서 넘겨야 하는데, 승계를 받는 사람이 다 떠안게 되거든요. 그래서 승계 때 내가고, 변경 신고 때는 나갈 때도 있고 안 나갈 때도 있는데, 거의 나가는 편이에요." / 송영욱: "어쨌든 지위승계가 끝나면 권리와 의무가 다 넘어가니까, 이전 분의 잘못을 승계받은 분이 처벌까지 다 떠안게 되는 거죠." / 송영욱: "비전자인 지위승계 같은 경우는 직접 서류를 뽑아서 접수하러 오세요. 그럴 때 바로 접수를 안 하고, 민원실에서 접수하고 오시게 하거나 접수해 놓고 가시게 해요." / 송영욱: "지위승계 현장 확인을 가면, 현장이 가까우면 괜찮은데 20~30킬로미터 떨어져 있으면 하루 안에 못 갈 때도 있어요." / 송영욱: "지위승계 할 때 등기 관련 서류(토지 등기, 건물 등기) 같은 거요. 그런 걸 꼭 받으시더라고요."</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>[현행 규정] 법 제14조제1항: 배출시설·처리시설을 양도하거나 설치자가 사망·합병한 경우 양수인 등이 지위를 승계(법률상 당연승계). 제3항: 승계한 자는 부령으로 정하는 바에 따라 시장·군수·구청장에게 신고. 시행규칙 제11조의3: 승계 사유 발생일부터 30일 이내에 별지 제7호서식 신고서에 설치허가증·설치신고증명서와 "그 밖에 변경내용을 확인할 수 있는 서류"를 첨부. 법 제11조제5항의 수리 의무는 제11조의 신고·변경신고에만 적용되고 제14조제3항 승계 신고에 대한 수리 규정은 없음. 그런데 별지 제7호서식(개정 2016.6.2.)은 처리기간 7일, 처리절차 접수→검토→결재→통지를 두고 작성방법 ⑭란에 "가축분뇨배출시설 설치신고 수리일"을 적도록 함. 승계신고 미이행은 제53조제3항제4호 과태료.
 [문제점] ① 법률상 제14조제3항 신고는 수리 규정이 없는 사후 신고(30일 이내)로 행정절차법 제40조제2항에 따라 형식 요건을 갖추어 도달하면 의무가 이행되는 구조인데, 서식은 7일 처리와 통지를 전제하고 안동시는 승계 신고 시 현장 확인을 거쳐 처리(현장이 멀면 하루 안에 확인 불가, 기한 압박, 접수 시점 조정) → 신고의 법적 성격과 서식·실무 절차가 어긋나고 신고인은 승계 효력의 발생 시점을 알기 어려움. ② 승계는 당연승계이므로 양도인의 변경신고 미이행·불법 증축에 대한 책임이 양수인에게 넘어가는데, 승계 신고 단계에서 행정청이 위반사항을 확인하거나 양수인에게 알리는 절차가 법령에 없어 담당자가 임의로 현장 확인을 하고 있음. ③ 첨부서류 "그 밖에 변경내용을 확인할 수 있는 서류"가 포괄적이어서 전임자처럼 등기 서류 등 법정 외 서류를 요구하는 통로가 됨(민원처리법 제10조, 검토메모 참조).
@@ -1014,7 +865,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>제외기준 1(법정 서류 외 요구는 일반법 위반 소지의 운영 문제). 부수 정비 검토 가능: 별지 제5호·제7호서식에 행정정보 공동이용 확인란(토지·건축물대장 등) 신설 및 시행규칙 제11조의3 첨부서류의 특정(연번 10 안1과 연계). 지위승계 신고서식의 '공증 받은 양도·양수계약서' 요구는 신고인 부담이나 인터뷰에서 제기되지 않아 기록만 함.</t>
+          <t>제외기준 1(법정 서류 외 요구는 일반법 위반 소지의 운영 문제). 부수 정비 검토 가능: 별지 제5호·제7호서식에 행정정보 공동이용 확인란(토지·건축물대장 등) 신설 및 시행규칙 제11조의3 첨부서류의 특정(연번 6 안1과 연계). 지위승계 신고서식의 '공증 받은 양도·양수계약서' 요구는 신고인 부담이나 인터뷰에서 제기되지 않아 기록만 함.</t>
         </is>
       </c>
     </row>
@@ -1040,7 +891,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>발언은 고치지 않고 차이만 기록. 연번 1·2의 문제점 ②(서식 의존으로 인한 인지 혼선) 근거.</t>
+          <t>발언은 고치지 않고 차이만 기록. 연번 1의 문제점 ②(서식 의존으로 인한 인지 혼선) 근거.</t>
         </is>
       </c>
     </row>
@@ -1118,7 +969,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>처분 효과 승계 조항 신설은 제재 측면이 있어 본표 제외(제외기준 3). 양수인에게 위반사항을 알리는 절차는 연번 10 개정 방향에 반영.</t>
+          <t>처분 효과 승계 조항 신설은 제재 측면이 있어 본표 제외(제외기준 3). 양수인에게 위반사항을 알리는 절차는 연번 6 개정 방향에 반영.</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1255,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>연번 3·4의 배경 자료. 부칙 원문은 미대조.</t>
+          <t>연번 2의 배경 자료. 부칙 원문은 미대조.</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1488,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>제33조 원문 확인. 제4항·제5항(신고수리 통지기한·수리 간주) &lt;신설 2018.10.16.&gt; — 연번 1·2·10의 입법례. 부령상 기간은 미확인.</t>
+          <t>제33조 원문 확인. 제4항·제5항(신고수리 통지기한·수리 간주) &lt;신설 2018.10.16.&gt; — 연번 1·6의 입법례. 부령상 기간은 미확인.</t>
         </is>
       </c>
     </row>
